--- a/Documentation/Game Progression.xlsx
+++ b/Documentation/Game Progression.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\Rock_Paper_Scissors_Repo\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EEC0A7D-6445-4A11-BA20-A991712C1EDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33FBE56A-8BED-4EB7-BE8C-01C48F218D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -159,14 +159,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -278,24 +290,24 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>'Game Progression'!$K$2:$K$21</c:f>
+              <c:f>'Game Progression'!$K$2:$K$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6</c:v>
@@ -307,40 +319,52 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>6</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>7</c:v>
-                </c:pt>
                 <c:pt idx="10">
-                  <c:v>7</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>6</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>8</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>10</c:v>
                 </c:pt>
-                <c:pt idx="14">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
                   <c:v>12</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="18">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>14</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="21">
                   <c:v>16</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="22">
                   <c:v>17</c:v>
                 </c:pt>
-                <c:pt idx="19">
-                  <c:v>17</c:v>
+                <c:pt idx="23">
+                  <c:v>18</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -380,10 +404,10 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>'Game Progression'!$P$2:$P$21</c:f>
+              <c:f>'Game Progression'!$P$2:$P$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>4</c:v>
                 </c:pt>
@@ -421,28 +445,40 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>16</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="18">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="23">
                   <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>22</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1216,15 +1252,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>866775</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>14287</xdr:rowOff>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>23812</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>90487</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>771525</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>100012</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1515,7 +1551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA21"/>
+  <dimension ref="A1:AA25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" customWidth="1"/>
@@ -1628,13 +1664,12 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <f>C2-D2-G2</f>
         <v>1</v>
       </c>
       <c r="F2">
@@ -1645,18 +1680,18 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
         <f>H2*$T$2+G2*$V$2+C2*$U$2+L2*$W$2</f>
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="K2">
         <f>H2-I2</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -1669,7 +1704,7 @@
       </c>
       <c r="O2">
         <f>M2+N2-J2</f>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P2">
         <f>R2-Q2</f>
@@ -1731,18 +1766,18 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <f t="shared" ref="J3:J21" si="0">H3*$T$2+G3*$V$2+C3*$U$2+L3*$W$2</f>
-        <v>50</v>
+        <f t="shared" ref="J3:J25" si="0">H3*$T$2+G3*$V$2+C3*$U$2+L3*$W$2</f>
+        <v>100</v>
       </c>
       <c r="K3">
         <f>K2-I3+H3</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -1780,29 +1815,29 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <f t="shared" ref="E4:E21" si="1">C4+E3-G4</f>
+        <f t="shared" ref="E4:E25" si="1">C4+E3-G4</f>
         <v>1</v>
       </c>
       <c r="F4">
-        <f t="shared" ref="F4:F21" si="2">F3+G4-D4</f>
+        <f t="shared" ref="F4:F25" si="2">F3+G4-D4</f>
         <v>0</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4:K21" si="3">K3-I4+H4</f>
-        <v>3</v>
+        <f t="shared" ref="K4:K25" si="3">K3-I4+H4</f>
+        <v>4</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1811,15 +1846,15 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <f t="shared" ref="N4:N21" si="4">B4*$Y$2+E4*$Z$2+Q4*$X$2+F4*$AA$2</f>
+        <f t="shared" ref="N4:N25" si="4">B4*$Y$2+E4*$Z$2+Q4*$X$2+F4*$AA$2</f>
         <v>60</v>
       </c>
       <c r="O4">
-        <f t="shared" ref="O4:O21" si="5">O3+M4+N4-J4</f>
-        <v>50</v>
+        <f t="shared" ref="O4:O25" si="5">O3+M4+N4-J4</f>
+        <v>100</v>
       </c>
       <c r="P4">
-        <f t="shared" ref="P4:P21" si="6">P3+R4-Q4</f>
+        <f t="shared" ref="P4:P25" si="6">P3+R4-Q4</f>
         <v>2</v>
       </c>
       <c r="Q4">
@@ -1862,7 +1897,7 @@
       </c>
       <c r="K5" s="1">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5" s="1">
         <v>0</v>
@@ -1876,7 +1911,7 @@
       </c>
       <c r="O5" s="1">
         <f t="shared" si="5"/>
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="P5" s="1">
         <f t="shared" si="6"/>
@@ -1922,13 +1957,13 @@
       </c>
       <c r="K6">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <f t="shared" si="4"/>
@@ -1936,7 +1971,7 @@
       </c>
       <c r="O6">
         <f t="shared" si="5"/>
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="P6">
         <f t="shared" si="6"/>
@@ -1974,14 +2009,14 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K7">
         <f t="shared" si="3"/>
@@ -2154,24 +2189,24 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
         <f t="shared" si="0"/>
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="K10">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>1</v>
       </c>
       <c r="M10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N10">
         <f t="shared" si="4"/>
@@ -2179,7 +2214,7 @@
       </c>
       <c r="O10">
         <f t="shared" si="5"/>
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="P10">
         <f t="shared" si="6"/>
@@ -2228,7 +2263,7 @@
       </c>
       <c r="K11">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L11">
         <v>1</v>
@@ -2242,7 +2277,7 @@
       </c>
       <c r="O11">
         <f t="shared" si="5"/>
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="P11">
         <f t="shared" si="6"/>
@@ -2277,18 +2312,18 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12">
         <v>1</v>
       </c>
       <c r="J12">
         <f t="shared" si="0"/>
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="K12">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>1</v>
@@ -2348,7 +2383,7 @@
       </c>
       <c r="K13" s="1">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L13" s="1">
         <v>1</v>
@@ -2408,13 +2443,13 @@
       </c>
       <c r="K14">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>1</v>
       </c>
       <c r="M14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N14">
         <f t="shared" si="4"/>
@@ -2422,17 +2457,17 @@
       </c>
       <c r="O14">
         <f t="shared" si="5"/>
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="P14">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Q14">
         <v>2</v>
       </c>
       <c r="R14">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
@@ -2471,7 +2506,7 @@
       </c>
       <c r="K15">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -2485,11 +2520,11 @@
       </c>
       <c r="O15">
         <f t="shared" si="5"/>
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="P15">
         <f t="shared" si="6"/>
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q15">
         <v>2</v>
@@ -2531,7 +2566,7 @@
       </c>
       <c r="K16">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -2545,17 +2580,17 @@
       </c>
       <c r="O16">
         <f t="shared" si="5"/>
-        <v>140</v>
+        <v>40</v>
       </c>
       <c r="P16">
         <f t="shared" si="6"/>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Q16">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -2580,18 +2615,18 @@
         <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I17" s="1">
         <v>1</v>
       </c>
       <c r="J17" s="1">
         <f t="shared" si="0"/>
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="K17" s="1">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L17" s="1">
         <v>1</v>
@@ -2609,13 +2644,13 @@
       </c>
       <c r="P17" s="1">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q17" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2651,13 +2686,13 @@
       </c>
       <c r="K18">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L18">
         <v>1</v>
       </c>
       <c r="M18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N18">
         <f t="shared" si="4"/>
@@ -2665,20 +2700,20 @@
       </c>
       <c r="O18">
         <f t="shared" si="5"/>
-        <v>140</v>
+        <v>40</v>
       </c>
       <c r="P18">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="Q18">
         <v>2</v>
       </c>
       <c r="R18">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2714,7 +2749,7 @@
       </c>
       <c r="K19">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -2724,21 +2759,21 @@
       </c>
       <c r="N19">
         <f t="shared" si="4"/>
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="O19">
         <f t="shared" si="5"/>
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="P19">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="Q19">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2774,7 +2809,7 @@
       </c>
       <c r="K20">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -2784,21 +2819,21 @@
       </c>
       <c r="N20">
         <f t="shared" si="4"/>
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="O20">
         <f t="shared" si="5"/>
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="P20">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q20">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -2823,18 +2858,18 @@
         <v>1</v>
       </c>
       <c r="H21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" s="1">
         <v>1</v>
       </c>
       <c r="J21" s="1">
         <f t="shared" si="0"/>
-        <v>270</v>
+        <v>220</v>
       </c>
       <c r="K21" s="1">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="L21" s="1">
         <v>1</v>
@@ -2844,29 +2879,281 @@
       </c>
       <c r="N21" s="1">
         <f t="shared" si="4"/>
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="O21" s="1">
         <f t="shared" si="5"/>
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="P21" s="1">
         <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>2</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="L22" s="2">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="O22">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+      <c r="P22">
+        <f t="shared" si="6"/>
+        <v>26</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>2</v>
+      </c>
+      <c r="R22">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="Q21" s="1">
-        <v>2</v>
-      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>2</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="L23" s="2">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <f t="shared" si="4"/>
+        <v>140</v>
+      </c>
+      <c r="O23">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="P23">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="Q23" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>2</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="L24" s="2">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <f t="shared" si="4"/>
+        <v>140</v>
+      </c>
+      <c r="O24">
+        <f t="shared" si="5"/>
+        <v>140</v>
+      </c>
+      <c r="P24">
+        <f t="shared" si="6"/>
+        <v>18</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1">
+        <v>1</v>
+      </c>
+      <c r="C25" s="3">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3">
+        <v>0</v>
+      </c>
+      <c r="E25" s="1">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="F25" s="1">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>2</v>
+      </c>
+      <c r="I25" s="1">
+        <v>1</v>
+      </c>
+      <c r="J25" s="1">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="K25" s="1">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="1">
+        <f t="shared" si="4"/>
+        <v>140</v>
+      </c>
+      <c r="O25" s="1">
+        <f t="shared" si="5"/>
+        <v>180</v>
+      </c>
+      <c r="P25" s="1">
+        <f t="shared" si="6"/>
+        <v>14</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>4</v>
+      </c>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
+      <c r="U25" s="1"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H50">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
       <formula>B2+E2+F2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I22:I25">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+      <formula>C22+F22+G22</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
